--- a/results/assessment/vIAbility/features/markers/ML/iter4/cv_results.xlsx
+++ b/results/assessment/vIAbility/features/markers/ML/iter4/cv_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -558,646 +558,560 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GaussianNB</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5454</v>
+        <v>0.5028</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4357</v>
+        <v>0.2328</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4029</v>
+        <v>0.4435</v>
       </c>
       <c r="E3" t="n">
-        <v>0.426</v>
+        <v>0.2466</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4148</v>
+        <v>0.2841</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5049</v>
+        <v>0.4689</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0417</v>
+        <v>0.0832</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0537</v>
+        <v>0.1909</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.4613</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0558</v>
+        <v>0.2079</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0669</v>
+        <v>0.2572</v>
       </c>
       <c r="M3" t="n">
-        <v>0.057</v>
+        <v>0.0736</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5346</v>
+        <v>0.5454</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4177</v>
+        <v>0.4357</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4087</v>
+        <v>0.4029</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4144</v>
+        <v>0.426</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4111</v>
+        <v>0.4148</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5141</v>
+        <v>0.5049</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0398</v>
+        <v>0.0417</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0703</v>
+        <v>0.0537</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1042</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0775</v>
+        <v>0.0558</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0669</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0476</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLPClassifier</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3959</v>
+        <v>0.5346</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3743</v>
+        <v>0.4177</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.4087</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4124</v>
+        <v>0.4144</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4886</v>
+        <v>0.4111</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4658</v>
+        <v>0.5141</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0574</v>
+        <v>0.0398</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0251</v>
+        <v>0.0703</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1306</v>
+        <v>0.1042</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0281</v>
+        <v>0.0775</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0446</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0477</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>MLPClassifier</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4963</v>
+        <v>0.3959</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4049</v>
+        <v>0.3743</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4957</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4196</v>
+        <v>0.4124</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4445</v>
+        <v>0.4886</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.4658</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0473</v>
+        <v>0.0574</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0415</v>
+        <v>0.0251</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0497</v>
+        <v>0.1306</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0391</v>
+        <v>0.0281</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0379</v>
+        <v>0.0446</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0446</v>
+        <v>0.0477</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TabPFN</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5904</v>
+        <v>0.4963</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1143</v>
+        <v>0.4049</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0348</v>
+        <v>0.4957</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0784</v>
+        <v>0.4196</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0533</v>
+        <v>0.4445</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5014</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0148</v>
+        <v>0.0473</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2286</v>
+        <v>0.0415</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0696</v>
+        <v>0.0497</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1569</v>
+        <v>0.0391</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1067</v>
+        <v>0.0379</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0506</v>
+        <v>0.0446</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bagging_RandomForest</t>
+          <t>TabPFN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5206</v>
+        <v>0.5904</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3663</v>
+        <v>0.1143</v>
       </c>
       <c r="D8" t="n">
-        <v>0.238</v>
+        <v>0.0348</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3292</v>
+        <v>0.0784</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2871</v>
+        <v>0.0533</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4325</v>
+        <v>0.5014</v>
       </c>
       <c r="H8" t="n">
-        <v>0.064</v>
+        <v>0.0148</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1092</v>
+        <v>0.2286</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0742</v>
+        <v>0.0696</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0983</v>
+        <v>0.1569</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0868</v>
+        <v>0.1067</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0506</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bagging_SVC</t>
+          <t>Bagging_RandomForest</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5</v>
+        <v>0.5206</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1459</v>
+        <v>0.3663</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3304</v>
+        <v>0.238</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1641</v>
+        <v>0.3292</v>
       </c>
       <c r="F9" t="n">
-        <v>0.202</v>
+        <v>0.2871</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4828</v>
+        <v>0.4325</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1124</v>
+        <v>0.064</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1804</v>
+        <v>0.1092</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4194</v>
+        <v>0.0742</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2032</v>
+        <v>0.0983</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2513</v>
+        <v>0.0868</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0509</v>
+        <v>0.06270000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bagging_GaussianNB</t>
+          <t>Bagging_SVC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5279</v>
+        <v>0.5</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4147</v>
+        <v>0.1459</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3757</v>
+        <v>0.3304</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4059</v>
+        <v>0.1641</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3937</v>
+        <v>0.202</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5131</v>
+        <v>0.4828</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0416</v>
+        <v>0.1124</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0549</v>
+        <v>0.1804</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0264</v>
+        <v>0.4194</v>
       </c>
       <c r="K10" t="n">
-        <v>0.048</v>
+        <v>0.2032</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0388</v>
+        <v>0.2513</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0649</v>
+        <v>0.0509</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bagging_DecisionTree</t>
+          <t>Bagging_GaussianNB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4929</v>
+        <v>0.5279</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3281</v>
+        <v>0.4147</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2308</v>
+        <v>0.3757</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2989</v>
+        <v>0.4059</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2666</v>
+        <v>0.3937</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4342</v>
+        <v>0.5131</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0499</v>
+        <v>0.0416</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0735</v>
+        <v>0.0549</v>
       </c>
       <c r="J11" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0264</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0641</v>
+        <v>0.048</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0619</v>
+        <v>0.0388</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0583</v>
+        <v>0.0649</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bagging_MLPClassifier</t>
+          <t>Bagging_DecisionTree</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v/>
+        <v>0.4929</v>
       </c>
       <c r="C12" t="n">
-        <v/>
+        <v>0.3281</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>0.2308</v>
       </c>
       <c r="E12" t="n">
-        <v/>
+        <v>0.2989</v>
       </c>
       <c r="F12" t="n">
-        <v/>
+        <v>0.2666</v>
       </c>
       <c r="G12" t="n">
-        <v/>
+        <v>0.4342</v>
       </c>
       <c r="H12" t="n">
-        <v/>
+        <v>0.0499</v>
       </c>
       <c r="I12" t="n">
-        <v/>
+        <v>0.0735</v>
       </c>
       <c r="J12" t="n">
-        <v/>
+        <v>0.07049999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v/>
+        <v>0.0641</v>
       </c>
       <c r="L12" t="n">
-        <v/>
+        <v>0.0619</v>
       </c>
       <c r="M12" t="n">
-        <v/>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bagging_LogisticRegression</t>
+          <t>Bagging_MLPClassifier</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5243</v>
+        <v/>
       </c>
       <c r="C13" t="n">
-        <v>0.4206</v>
+        <v/>
       </c>
       <c r="D13" t="n">
-        <v>0.4192</v>
+        <v/>
       </c>
       <c r="E13" t="n">
-        <v>0.4191</v>
+        <v/>
       </c>
       <c r="F13" t="n">
-        <v>0.4181</v>
+        <v/>
       </c>
       <c r="G13" t="n">
-        <v>0.4981</v>
+        <v/>
       </c>
       <c r="H13" t="n">
-        <v>0.0504</v>
+        <v/>
       </c>
       <c r="I13" t="n">
-        <v>0.0503</v>
+        <v/>
       </c>
       <c r="J13" t="n">
-        <v>0.036</v>
+        <v/>
       </c>
       <c r="K13" t="n">
-        <v>0.0412</v>
+        <v/>
       </c>
       <c r="L13" t="n">
-        <v>0.033</v>
+        <v/>
       </c>
       <c r="M13" t="n">
-        <v>0.0557</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bagging_TabPFN</t>
+          <t>Bagging_LogisticRegression</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5243</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2686</v>
+        <v>0.4206</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0428</v>
+        <v>0.4192</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1248</v>
+        <v>0.4191</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0721</v>
+        <v>0.4181</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4341</v>
+        <v>0.4981</v>
       </c>
       <c r="H14" t="n">
-        <v>0.026</v>
+        <v>0.0504</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1223</v>
+        <v>0.0503</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0009</v>
+        <v>0.036</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0189</v>
+        <v>0.0412</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0034</v>
+        <v>0.033</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0507</v>
+        <v>0.0557</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Voting_soft_SVC+MLPClassifier</t>
+          <t>Bagging_TabPFN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.49</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.388</v>
+        <v>0.2686</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4192</v>
+        <v>0.0428</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3914</v>
+        <v>0.1248</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3986</v>
+        <v>0.0721</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4698</v>
+        <v>0.4341</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0849</v>
+        <v>0.026</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0775</v>
+        <v>0.1223</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1055</v>
+        <v>0.0009</v>
       </c>
       <c r="K15" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0189</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0793</v>
+        <v>0.0034</v>
       </c>
       <c r="M15" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Voting_soft_MLPClassifier+TabPFN</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5142</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.3719</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.2833</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.3307</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.3046</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.0607</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.0752</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.1335</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.0931</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.0683</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Voting_soft_RandomForest+SVC+DecisionTree+TabPFN</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.5381</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.4087</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.4127</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.0364</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.06859999999999999</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.1042</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.0765</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.08749999999999999</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.0526</v>
+        <v>0.0507</v>
       </c>
     </row>
   </sheetData>
@@ -1211,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1608,156 +1522,6 @@
       </c>
       <c r="G15" t="n">
         <v>0.5799</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Voting_hard_SVC+MLPClassifier</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5714</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Voting_hard_SVC+MLPClassifier+TabPFN</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.5714</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Voting_hard_SVC+DecisionTree+MLPClassifier</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.5275</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.4444</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.4103</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.4372</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.4267</v>
-      </c>
-      <c r="G18" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Voting_soft_SVC+MLPClassifier</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.5824</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.5094</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.6923</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.5377999999999999</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.5661</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Voting_soft_MLPClassifier+TabPFN</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.5824</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.5172</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.3846</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.4839</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.4412</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.6188</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Voting_soft_RandomForest+SVC+DecisionTree+TabPFN</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.4835</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.4048</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.4359</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.4106</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.4198</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.5217000000000001</v>
       </c>
     </row>
   </sheetData>
